--- a/(枠)◯年度一式/ウニガラ(サケ）.xlsx
+++ b/(枠)◯年度一式/ウニガラ(サケ）.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{521F44EC-AB7B-4D7C-A9CD-D3E90268C1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09C35A0-707D-455B-B988-30706AB24313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="720" windowWidth="19305" windowHeight="15480" activeTab="5" xr2:uid="{DEC9D196-2D5E-46FA-B56B-3B2E57D6F36C}"/>
+    <workbookView xWindow="13785" yWindow="0" windowWidth="13215" windowHeight="15480" activeTab="5" xr2:uid="{DEC9D196-2D5E-46FA-B56B-3B2E57D6F36C}"/>
   </bookViews>
   <sheets>
     <sheet name="06" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="26">
   <si>
     <t>亀田建設</t>
     <rPh sb="0" eb="2">
@@ -254,38 +254,6 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
-  <si>
-    <t>30年度ウニガラ受入れ簿</t>
-    <rPh sb="2" eb="3">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ウケイ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ボ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>30年度ウニガラ受入れ実績表</t>
-    <rPh sb="2" eb="4">
-      <t>ネンド</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ウケイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ジッセキ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
 </sst>
 </file>
 
@@ -293,7 +261,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
-    <numFmt numFmtId="178" formatCode="#,##0;[Red]#,##0"/>
+    <numFmt numFmtId="177" formatCode="#,##0;[Red]#,##0"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -515,7 +483,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -679,35 +647,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="10"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color indexed="12"/>
-      </font>
-    </dxf>
+  <dxfs count="34">
     <dxf>
       <font>
         <condense val="0"/>
@@ -966,16 +906,38 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sheet1"/>
+      <sheetName val="A-1"/>
+      <sheetName val="A-2"/>
+      <sheetName val="B-1"/>
+      <sheetName val="収集（全般）"/>
+      <sheetName val="可燃"/>
+      <sheetName val="不燃・木くず・海岸清掃"/>
+      <sheetName val="ビン類"/>
+      <sheetName val="缶類"/>
+      <sheetName val="ペットボトル"/>
+      <sheetName val="紙類"/>
+      <sheetName val="粗大"/>
+      <sheetName val="産廃水産・医療・汚泥"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="C2">
-            <v>8</v>
+        <row r="9">
+          <cell r="E9">
+            <v>2027</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1277,8 +1239,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="53" t="s">
-        <v>26</v>
+      <c r="A1" s="53" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度ウニガラ受入れ簿"</f>
+        <v>令和9年度ウニガラ受入れ簿</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -1850,44 +1813,36 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="expression" dxfId="37" priority="9" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A35))=7</formula>
+  <conditionalFormatting sqref="A5:A6">
+    <cfRule type="expression" dxfId="33" priority="1" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A5))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="10" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A35))=1</formula>
+    <cfRule type="expression" dxfId="32" priority="2" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A5))=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:A11 A14:A18 A21:A25 A28:A32">
-    <cfRule type="expression" dxfId="35" priority="15" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="15" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2013,$A$2,A7))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="16" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2013,$A$2,A7))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A27 A33:A34">
-    <cfRule type="expression" dxfId="33" priority="5" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A26))=7</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="6" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A26))=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A12:A13 A19:A20">
-    <cfRule type="expression" dxfId="31" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="3" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2011,$A$2,A12))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="4" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2011,$A$2,A12))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A6">
-    <cfRule type="expression" dxfId="29" priority="1" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A5))=7</formula>
+  <conditionalFormatting sqref="A26:A27 A33:A35">
+    <cfRule type="expression" dxfId="27" priority="5" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A26))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="2" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A5))=1</formula>
+    <cfRule type="expression" dxfId="26" priority="6" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A26))=1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -1914,7 +1869,7 @@
     <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="53" t="str">
         <f>'06'!A1:H1</f>
-        <v>30年度ウニガラ受入れ簿</v>
+        <v>令和9年度ウニガラ受入れ簿</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -2488,28 +2443,20 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A20:A23 A5:A9 A12:A16 A26:A30 A33:A35">
-    <cfRule type="expression" dxfId="27" priority="13" stopIfTrue="1">
+  <conditionalFormatting sqref="A5:A9 A12:A16 A26:A30 A33:A35">
+    <cfRule type="expression" dxfId="25" priority="13" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2013,$A$2,A5))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="14" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="14" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2013,$A$2,A5))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32">
-    <cfRule type="expression" dxfId="25" priority="11" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A32))=7</formula>
+  <conditionalFormatting sqref="A10:A11">
+    <cfRule type="expression" dxfId="23" priority="5" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A10))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="12" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A32))=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A31">
-    <cfRule type="expression" dxfId="23" priority="9" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A31))=7</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="10" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A31))=1</formula>
+    <cfRule type="expression" dxfId="22" priority="6" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A10))=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17:A18 A24:A25">
@@ -2520,20 +2467,20 @@
       <formula>WEEKDAY(DATE(2011,$A$2,A17))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:A11">
-    <cfRule type="expression" dxfId="19" priority="5" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A10))=7</formula>
+  <conditionalFormatting sqref="A19:A23">
+    <cfRule type="expression" dxfId="19" priority="1" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2013,$A$2,A19))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="6" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A10))=1</formula>
+    <cfRule type="expression" dxfId="18" priority="2" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2013,$A$2,A19))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="expression" dxfId="17" priority="1" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2013,$A$2,A19))=7</formula>
+  <conditionalFormatting sqref="A31:A32">
+    <cfRule type="expression" dxfId="17" priority="9" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A31))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2013,$A$2,A19))=1</formula>
+    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A31))=1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2560,7 +2507,7 @@
     <row r="1" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="53" t="str">
         <f>'06'!A1:H1</f>
-        <v>30年度ウニガラ受入れ簿</v>
+        <v>令和9年度ウニガラ受入れ簿</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -3143,7 +3090,7 @@
       <formula>WEEKDAY(DATE(2013,$A$2,A5))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:A22 A14:A15 A7:A8">
+  <conditionalFormatting sqref="A7:A8 A14:A15 A21:A22">
     <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2011,$A$2,A7))=7</formula>
     </cfRule>
@@ -3151,7 +3098,7 @@
       <formula>WEEKDAY(DATE(2011,$A$2,A7))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35 A28:A29">
+  <conditionalFormatting sqref="A28:A29 A35">
     <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2011,$A$2,A28))=7</formula>
     </cfRule>
@@ -3183,7 +3130,7 @@
     <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="53" t="str">
         <f>'06'!A1:H1</f>
-        <v>30年度ウニガラ受入れ簿</v>
+        <v>令和9年度ウニガラ受入れ簿</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
@@ -3761,31 +3708,31 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="A21:A24 A28:A31 A6:A10 A13:A17 A34">
-    <cfRule type="expression" dxfId="9" priority="9" stopIfTrue="1">
+  <conditionalFormatting sqref="A5 A11:A12 A18:A19">
+    <cfRule type="expression" dxfId="9" priority="5" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A5))=7</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="6" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A5))=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:A10 A13:A17 A28:A31 A34">
+    <cfRule type="expression" dxfId="7" priority="9" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2013,$A$2,A6))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="10" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2013,$A$2,A6))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A27 A32:A33">
-    <cfRule type="expression" dxfId="7" priority="7" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A26))=7</formula>
+  <conditionalFormatting sqref="A20:A24">
+    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2013,$A$2,A20))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="8" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A26))=1</formula>
+    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2013,$A$2,A20))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5 A11:A12 A18:A19">
-    <cfRule type="expression" dxfId="5" priority="5" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A5))=7</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2011,$A$2,A5))=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
+  <conditionalFormatting sqref="A25:A27">
     <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
       <formula>WEEKDAY(DATE(2011,$A$2,A25))=7</formula>
     </cfRule>
@@ -3793,12 +3740,12 @@
       <formula>WEEKDAY(DATE(2011,$A$2,A25))=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2013,$A$2,A20))=7</formula>
+  <conditionalFormatting sqref="A32:A33">
+    <cfRule type="expression" dxfId="1" priority="7" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A32))=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>WEEKDAY(DATE(2013,$A$2,A20))=1</formula>
+    <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
+      <formula>WEEKDAY(DATE(2011,$A$2,A32))=1</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -3822,8 +3769,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="57" t="s">
-        <v>27</v>
+      <c r="A1" s="57" t="str">
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度ウニガラ受入れ実績表"</f>
+        <v>令和9年度ウニガラ受入れ実績表</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4102,8 +4050,8 @@
   <sheetData>
     <row r="1" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="58" t="str">
-        <f>"令和"&amp;[1]Sheet1!$C$2&amp;"年度さけ残渣受入れ簿"</f>
-        <v>令和8年度さけ残渣受入れ簿</v>
+        <f>"令和"&amp;'[1]A-1'!$E$9-2018&amp;"年度さけ残渣受入れ簿"</f>
+        <v>令和9年度さけ残渣受入れ簿</v>
       </c>
       <c r="B1" s="58"/>
       <c r="C1" s="58"/>

--- a/(枠)◯年度一式/ウニガラ(サケ）.xlsx
+++ b/(枠)◯年度一式/ウニガラ(サケ）.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr updateLinks="always" defaultThemeVersion="124226"/>
+  <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09C35A0-707D-455B-B988-30706AB24313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A042127-0531-4881-890B-0E8E415D7D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13785" yWindow="0" windowWidth="13215" windowHeight="15480" activeTab="5" xr2:uid="{DEC9D196-2D5E-46FA-B56B-3B2E57D6F36C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{DEC9D196-2D5E-46FA-B56B-3B2E57D6F36C}"/>
   </bookViews>
   <sheets>
     <sheet name="06" sheetId="4" r:id="rId1"/>
